--- a/artfynd/A 44006-2024 artfynd.xlsx
+++ b/artfynd/A 44006-2024 artfynd.xlsx
@@ -1714,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120551954</v>
+        <v>120549919</v>
       </c>
       <c r="B11" t="n">
-        <v>91200</v>
+        <v>90114</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,38 +1726,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>5747</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654868</v>
+        <v>654959</v>
       </c>
       <c r="R11" t="n">
-        <v>6676580</v>
+        <v>6676476</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1789,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1810,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stor och gul. Skarp lukt av jordkällare. Kalkrik mark med kransmossa, fjällig taggsvamp och rödgul trumpetsvamp i närheten. Mest gran runtom. En tall 10 m bort.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,23 +1824,9 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1841,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120549813</v>
+        <v>120550122</v>
       </c>
       <c r="B12" t="n">
-        <v>91272</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,41 +1855,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654979</v>
+        <v>654939</v>
       </c>
       <c r="R12" t="n">
-        <v>6676460</v>
+        <v>6676616</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1916,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1926,7 +1936,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hörd till och från i skogen under ett par timmars tid. Gammal barrskog med både tall och gran ca 100-150 år, vissa tallar eventuellt äldre. Delar av skogen glesare men andra delar tätare och med flerskiktning. Ser över lag bra ut för talltita.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,21 +1952,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1964,14 +1964,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120550122</v>
+        <v>120551954</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>91200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,49 +1984,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654939</v>
+        <v>654868</v>
       </c>
       <c r="R13" t="n">
-        <v>6676616</v>
+        <v>6676580</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2051,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2061,12 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hörd till och från i skogen under ett par timmars tid. Gammal barrskog med både tall och gran ca 100-150 år, vissa tallar eventuellt äldre. Delar av skogen glesare men andra delar tätare och med flerskiktning. Ser över lag bra ut för talltita.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,6 +2068,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2089,18 +2095,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120549919</v>
+        <v>120549813</v>
       </c>
       <c r="B14" t="n">
-        <v>90114</v>
+        <v>91272</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2109,49 +2111,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5747</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654959</v>
+        <v>654979</v>
       </c>
       <c r="R14" t="n">
-        <v>6676476</v>
+        <v>6676460</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2183,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2193,12 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stor och gul. Skarp lukt av jordkällare. Kalkrik mark med kransmossa, fjällig taggsvamp och rödgul trumpetsvamp i närheten. Mest gran runtom. En tall 10 m bort.</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,9 +2193,23 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120551682</v>
+        <v>120553518</v>
       </c>
       <c r="B25" t="n">
-        <v>91512</v>
+        <v>105032</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3464,10 +3464,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654850</v>
+        <v>654888</v>
       </c>
       <c r="R25" t="n">
-        <v>6676525</v>
+        <v>6676732</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3509,12 +3509,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Kalkrik mark med gran runtom.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3541,10 +3536,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120553518</v>
+        <v>120546850</v>
       </c>
       <c r="B26" t="n">
-        <v>105032</v>
+        <v>91879</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3557,31 +3552,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3590,10 +3585,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654888</v>
+        <v>655091</v>
       </c>
       <c r="R26" t="n">
-        <v>6676732</v>
+        <v>6676379</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3625,7 +3620,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3635,7 +3630,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bara gran och asp i närheten. Närmaste tall &gt;30 m bort.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120546850</v>
+        <v>120551682</v>
       </c>
       <c r="B28" t="n">
-        <v>91879</v>
+        <v>91512</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3799,26 +3799,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655091</v>
+        <v>654850</v>
       </c>
       <c r="R28" t="n">
-        <v>6676379</v>
+        <v>6676525</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Bara gran och asp i närheten. Närmaste tall &gt;30 m bort.</t>
+          <t>Kalkrik mark med gran runtom.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4996,10 +4996,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120549857</v>
+        <v>120552970</v>
       </c>
       <c r="B38" t="n">
-        <v>91200</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5008,38 +5008,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654970</v>
+        <v>654913</v>
       </c>
       <c r="R38" t="n">
-        <v>6676469</v>
+        <v>6676611</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5071,7 +5080,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5081,7 +5090,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5092,21 +5101,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5123,10 +5117,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120552970</v>
+        <v>120552745</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5135,35 +5129,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5172,10 +5162,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654913</v>
+        <v>654817</v>
       </c>
       <c r="R39" t="n">
-        <v>6676611</v>
+        <v>6676682</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5207,7 +5197,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5217,7 +5207,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5228,6 +5218,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5244,10 +5249,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120552745</v>
+        <v>120549857</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>91200</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5256,43 +5261,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654817</v>
+        <v>654970</v>
       </c>
       <c r="R40" t="n">
-        <v>6676682</v>
+        <v>6676469</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5348,17 +5348,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120551702</v>
+        <v>120549606</v>
       </c>
       <c r="B41" t="n">
         <v>100194</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654817</v>
+        <v>655036</v>
       </c>
       <c r="R41" t="n">
-        <v>6676527</v>
+        <v>6676523</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5488,7 +5488,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120549606</v>
+        <v>120549116</v>
       </c>
       <c r="B42" t="n">
         <v>100194</v>
@@ -5521,17 +5521,26 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655036</v>
+        <v>655000</v>
       </c>
       <c r="R42" t="n">
-        <v>6676523</v>
+        <v>6676433</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5563,7 +5572,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5573,7 +5582,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5600,10 +5609,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120549116</v>
+        <v>120552287</v>
       </c>
       <c r="B43" t="n">
-        <v>100194</v>
+        <v>5189</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5616,31 +5625,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5649,10 +5654,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655000</v>
+        <v>654866</v>
       </c>
       <c r="R43" t="n">
-        <v>6676433</v>
+        <v>6676543</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5684,7 +5689,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5694,7 +5699,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5705,6 +5710,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5721,10 +5741,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120552287</v>
+        <v>120550648</v>
       </c>
       <c r="B44" t="n">
-        <v>5189</v>
+        <v>86351</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5733,43 +5753,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654866</v>
+        <v>654944</v>
       </c>
       <c r="R44" t="n">
-        <v>6676543</v>
+        <v>6676461</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5801,7 +5827,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5811,7 +5837,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Vid basen av en gammal gran på kalkrik mark. Tydligt kopparfärgad hatt. Ljust fruktkött och gula skivor. Ingen lukt alls, luktar inte ens "typisk svamp".</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5820,23 +5851,9 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5853,10 +5870,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120550648</v>
+        <v>120551702</v>
       </c>
       <c r="B45" t="n">
-        <v>86351</v>
+        <v>100194</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5865,49 +5882,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>445</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ruddu, Ruddu, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654944</v>
+        <v>654817</v>
       </c>
       <c r="R45" t="n">
-        <v>6676461</v>
+        <v>6676527</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5939,7 +5945,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5949,12 +5955,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Vid basen av en gammal gran på kalkrik mark. Tydligt kopparfärgad hatt. Ljust fruktkött och gula skivor. Ingen lukt alls, luktar inte ens "typisk svamp".</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5963,7 +5964,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44006-2024 artfynd.xlsx
+++ b/artfynd/A 44006-2024 artfynd.xlsx
@@ -6769,10 +6769,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120549921</v>
+        <v>120546850</v>
       </c>
       <c r="B53" t="n">
-        <v>91996</v>
+        <v>92006</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654960</v>
+        <v>655091</v>
       </c>
       <c r="R53" t="n">
-        <v>6676469</v>
+        <v>6676379</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6863,7 +6863,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Bara gran och asp i närheten. Närmaste tall &gt;30 m bort.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6890,10 +6895,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120546850</v>
+        <v>120549921</v>
       </c>
       <c r="B54" t="n">
-        <v>91996</v>
+        <v>92006</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6925,7 +6930,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6939,10 +6944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655091</v>
+        <v>654960</v>
       </c>
       <c r="R54" t="n">
-        <v>6676379</v>
+        <v>6676469</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6974,7 +6979,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6984,12 +6989,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Bara gran och asp i närheten. Närmaste tall &gt;30 m bort.</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 44006-2024 artfynd.xlsx
+++ b/artfynd/A 44006-2024 artfynd.xlsx
@@ -4699,11 +4699,11 @@
         <v>120550122</v>
       </c>
       <c r="B36" t="n">
-        <v>57501</v>
+        <v>57631</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">

--- a/artfynd/A 44006-2024 artfynd.xlsx
+++ b/artfynd/A 44006-2024 artfynd.xlsx
@@ -4699,7 +4699,7 @@
         <v>120550122</v>
       </c>
       <c r="B36" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
